--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98208</v>
+        <v>98211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
